--- a/artfynd/A 49053-2023 artfynd.xlsx
+++ b/artfynd/A 49053-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 49053-2023 artfynd.xlsx
+++ b/artfynd/A 49053-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1233,6 +1233,112 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128533096</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92742</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Öjvasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>406721</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6854885</v>
+      </c>
+      <c r="S7" t="n">
+        <v>8</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49053-2023 artfynd.xlsx
+++ b/artfynd/A 49053-2023 artfynd.xlsx
@@ -1238,7 +1238,7 @@
         <v>128533096</v>
       </c>
       <c r="B7" t="n">
-        <v>92742</v>
+        <v>92748</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 49053-2023 artfynd.xlsx
+++ b/artfynd/A 49053-2023 artfynd.xlsx
@@ -1238,7 +1238,7 @@
         <v>128533096</v>
       </c>
       <c r="B7" t="n">
-        <v>92748</v>
+        <v>92754</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 49053-2023 artfynd.xlsx
+++ b/artfynd/A 49053-2023 artfynd.xlsx
@@ -1238,7 +1238,7 @@
         <v>128533096</v>
       </c>
       <c r="B7" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 49053-2023 artfynd.xlsx
+++ b/artfynd/A 49053-2023 artfynd.xlsx
@@ -1238,7 +1238,7 @@
         <v>128533096</v>
       </c>
       <c r="B7" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 49053-2023 artfynd.xlsx
+++ b/artfynd/A 49053-2023 artfynd.xlsx
@@ -1238,7 +1238,7 @@
         <v>128533096</v>
       </c>
       <c r="B7" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 49053-2023 artfynd.xlsx
+++ b/artfynd/A 49053-2023 artfynd.xlsx
@@ -1238,7 +1238,7 @@
         <v>128533096</v>
       </c>
       <c r="B7" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 49053-2023 artfynd.xlsx
+++ b/artfynd/A 49053-2023 artfynd.xlsx
@@ -1238,7 +1238,7 @@
         <v>128533096</v>
       </c>
       <c r="B7" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 49053-2023 artfynd.xlsx
+++ b/artfynd/A 49053-2023 artfynd.xlsx
@@ -1238,7 +1238,7 @@
         <v>128533096</v>
       </c>
       <c r="B7" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 49053-2023 artfynd.xlsx
+++ b/artfynd/A 49053-2023 artfynd.xlsx
@@ -1238,7 +1238,7 @@
         <v>128533096</v>
       </c>
       <c r="B7" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 49053-2023 artfynd.xlsx
+++ b/artfynd/A 49053-2023 artfynd.xlsx
@@ -1238,7 +1238,7 @@
         <v>128533096</v>
       </c>
       <c r="B7" t="n">
-        <v>92806</v>
+        <v>92811</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 49053-2023 artfynd.xlsx
+++ b/artfynd/A 49053-2023 artfynd.xlsx
@@ -1238,7 +1238,7 @@
         <v>128533096</v>
       </c>
       <c r="B7" t="n">
-        <v>92811</v>
+        <v>92819</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 49053-2023 artfynd.xlsx
+++ b/artfynd/A 49053-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Vedsvampsinventering Sveaskog</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62439592</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Vedsvampsinventering Sveaskog</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62439591</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113887655</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1086,6 +1106,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128533096</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1192,6 +1217,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113887175</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1298,6 +1328,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113888050</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1404,8 +1439,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113887042</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>